--- a/data/NbiExampleOtnResources.xlsx
+++ b/data/NbiExampleOtnResources.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30030"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tan\repo\Ontology\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workshop\CmccOntology\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC59042-664B-42DA-82EE-561B0628ECC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE5A187-C84B-46E2-9F16-CBC9D18CCDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="676" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="676" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="资源对象清单" sheetId="45" r:id="rId1"/>
@@ -98,9 +98,6 @@
     <t>表示不关注</t>
   </si>
   <si>
-    <t>字符</t>
-  </si>
-  <si>
     <t>不在上述列表里的速率值，填其速率值，单位K或者M或者G，例如：25G、20M、64K
 注：当填写数字类型的字符时，默认单位为G。</t>
   </si>
@@ -148,9 +145,6 @@
   </si>
   <si>
     <t>HW</t>
-  </si>
-  <si>
-    <t>枚举</t>
   </si>
   <si>
     <t>网元rmUID</t>
@@ -173,9 +167,6 @@
     <t>OptiX OSN 8800</t>
   </si>
   <si>
-    <t>数字</t>
-  </si>
-  <si>
     <t>role</t>
   </si>
   <si>
@@ -359,6 +350,18 @@
   </si>
   <si>
     <t>STM64、odu2、ODU2e、OTU2、10GbE-WAN、ODU1f、10GE_LAN、STM64再生段、FC-1200(10G)、1xIB QDR、CPRI选项7、CPRI选项8、OTU2e、OTU1f、oduflex N=8</t>
+    <phoneticPr fontId="26" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="26" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum</t>
+    <phoneticPr fontId="26" type="noConversion"/>
+  </si>
+  <si>
+    <t>integer</t>
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
 </sst>
@@ -1104,7 +1107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1257,6 +1260,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1770,15 +1776,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25676CC-0FF8-4DDC-8886-831A15D3B0BF}">
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="8" customWidth="1"/>
-    <col min="2" max="2" width="22.88671875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="22.109375" style="8" customWidth="1"/>
-    <col min="5" max="8" width="8.77734375" style="8"/>
-    <col min="9" max="9" width="44.109375" style="8" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="8"/>
+    <col min="1" max="1" width="7.125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="22.875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="26.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="22.125" style="8" customWidth="1"/>
+    <col min="5" max="8" width="8.75" style="8"/>
+    <col min="9" max="9" width="44.125" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="8.75" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1786,13 +1792,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1800,13 +1806,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1814,13 +1820,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1828,13 +1834,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
@@ -1847,13 +1853,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
@@ -1872,159 +1878,159 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:F76"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.21875" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" customWidth="1"/>
-    <col min="5" max="5" width="97.21875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21.109375" customWidth="1"/>
-    <col min="8" max="8" width="19.109375" customWidth="1"/>
+    <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.25" customWidth="1"/>
+    <col min="3" max="3" width="19.5" customWidth="1"/>
+    <col min="4" max="4" width="15.25" customWidth="1"/>
+    <col min="5" max="5" width="97.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21.125" customWidth="1"/>
+    <col min="8" max="8" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="17.399999999999999">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="18.75">
+      <c r="A3" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" s="14" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="18.75">
+      <c r="A4" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="14" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
-      <c r="A3" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="19" t="s">
+    <row r="5" spans="1:5" ht="18.75">
+      <c r="A5" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="17.399999999999999">
-      <c r="A4" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="17.399999999999999">
-      <c r="A5" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="52.2">
+    </row>
+    <row r="6" spans="1:5" ht="36">
       <c r="A6" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="17.399999999999999">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18.75">
       <c r="A7" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="34.799999999999997">
+    <row r="8" spans="1:5" ht="18.75">
       <c r="A8" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17.399999999999999">
+    <row r="9" spans="1:5" ht="18.75">
       <c r="A9" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>3</v>
@@ -2036,29 +2042,29 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999">
+    <row r="10" spans="1:5" ht="18.75">
       <c r="A10" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17.399999999999999">
+    <row r="11" spans="1:5" ht="18.75">
       <c r="A11" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>3</v>
@@ -2070,12 +2076,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.399999999999999">
+    <row r="12" spans="1:5" ht="18.75">
       <c r="A12" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>3</v>
@@ -2087,12 +2093,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.399999999999999">
+    <row r="13" spans="1:5" ht="18.75">
       <c r="A13" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>3</v>
@@ -2104,12 +2110,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="17.399999999999999">
+    <row r="14" spans="1:5" ht="18.75">
       <c r="A14" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>3</v>
@@ -2121,12 +2127,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="17.399999999999999">
+    <row r="15" spans="1:5" ht="18.75">
       <c r="A15" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>3</v>
@@ -2138,12 +2144,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="17.399999999999999">
+    <row r="16" spans="1:5" ht="18.75">
       <c r="A16" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>3</v>
@@ -2155,12 +2161,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="17.399999999999999">
+    <row r="17" spans="1:5" ht="18.75">
       <c r="A17" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>3</v>
@@ -2172,21 +2178,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="34.799999999999997">
+    <row r="18" spans="1:5" ht="37.5">
       <c r="A18" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="3:6">
@@ -2244,58 +2250,58 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="33.33203125" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="33.375" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" style="32" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" style="40" customWidth="1"/>
-    <col min="3" max="3" width="22.77734375" style="41" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" style="32" customWidth="1"/>
-    <col min="6" max="6" width="16.88671875" style="32" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="54.5546875" style="42" customWidth="1"/>
+    <col min="1" max="1" width="7.625" style="32" customWidth="1"/>
+    <col min="2" max="2" width="18.375" style="40" customWidth="1"/>
+    <col min="3" max="3" width="22.75" style="41" customWidth="1"/>
+    <col min="4" max="4" width="18.5" style="32" customWidth="1"/>
+    <col min="5" max="5" width="16.125" style="32" customWidth="1"/>
+    <col min="6" max="6" width="16.875" style="32" customWidth="1"/>
+    <col min="7" max="7" width="21.5" style="40" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="54.5" style="42" customWidth="1"/>
     <col min="9" max="19" width="9" style="32" customWidth="1"/>
-    <col min="20" max="16384" width="33.33203125" style="32"/>
+    <col min="20" max="16384" width="33.375" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="32" customFormat="1" ht="34.799999999999997">
+    <row r="1" spans="1:8">
       <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="D1" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="E1" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="F1" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="G1" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="H1" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="37" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="32" customFormat="1">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="38">
         <v>1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">
@@ -2304,18 +2310,18 @@
       <c r="G2" s="39"/>
       <c r="H2" s="14"/>
     </row>
-    <row r="3" spans="1:8" s="32" customFormat="1">
+    <row r="3" spans="1:8">
       <c r="A3" s="38">
         <v>2</v>
       </c>
       <c r="B3" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="38" t="s">
-        <v>19</v>
+      <c r="D3" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="E3" s="38">
         <v>255</v>
@@ -2325,21 +2331,21 @@
       </c>
       <c r="G3" s="14"/>
       <c r="H3" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="32" customFormat="1" ht="52.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="56.25">
       <c r="A4" s="38">
         <v>3</v>
       </c>
       <c r="B4" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="38" t="s">
-        <v>19</v>
+      <c r="D4" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="E4" s="38">
         <v>255</v>
@@ -2349,21 +2355,21 @@
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="32" customFormat="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="38">
         <v>4</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="38" t="s">
-        <v>19</v>
+        <v>39</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="E5" s="38">
         <v>50</v>
@@ -2373,21 +2379,21 @@
       </c>
       <c r="G5" s="29"/>
       <c r="H5" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="32" customFormat="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="38">
         <v>5</v>
       </c>
       <c r="B6" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="38" t="s">
-        <v>19</v>
+      <c r="D6" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="E6" s="38">
         <v>20</v>
@@ -2397,21 +2403,21 @@
       </c>
       <c r="G6" s="14"/>
       <c r="H6" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="32" customFormat="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="38">
         <v>22</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="E7" s="38"/>
       <c r="F7" s="38" t="s">
@@ -2419,7 +2425,7 @@
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2441,43 +2447,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" style="32" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" style="32" customWidth="1"/>
-    <col min="3" max="3" width="26.5546875" style="32" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="6.625" style="32" customWidth="1"/>
+    <col min="2" max="2" width="16.75" style="32" customWidth="1"/>
+    <col min="3" max="3" width="26.5" style="32" customWidth="1"/>
+    <col min="4" max="4" width="19.5" style="32" customWidth="1"/>
     <col min="5" max="5" width="18" style="32" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" style="32" customWidth="1"/>
-    <col min="7" max="7" width="24.6640625" style="48" customWidth="1"/>
-    <col min="8" max="8" width="55.33203125" style="42" customWidth="1"/>
-    <col min="9" max="16384" width="8.77734375" style="32"/>
+    <col min="6" max="6" width="14.5" style="32" customWidth="1"/>
+    <col min="7" max="7" width="24.625" style="48" customWidth="1"/>
+    <col min="8" max="8" width="55.375" style="42" customWidth="1"/>
+    <col min="9" max="16384" width="8.75" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="32" customFormat="1" ht="34.799999999999997">
+    <row r="1" spans="1:8">
       <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="D1" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="E1" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="F1" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="G1" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="H1" s="43" t="s">
         <v>26</v>
-      </c>
-      <c r="H1" s="43" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="46" customFormat="1">
@@ -2485,13 +2491,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">
@@ -2500,18 +2506,18 @@
       <c r="G2" s="29"/>
       <c r="H2" s="45"/>
     </row>
-    <row r="3" spans="1:8" s="32" customFormat="1">
+    <row r="3" spans="1:8">
       <c r="A3" s="44">
         <v>2</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="47" t="s">
-        <v>19</v>
+        <v>45</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="E3" s="47"/>
       <c r="F3" s="47" t="s">
@@ -2520,18 +2526,18 @@
       <c r="G3" s="29"/>
       <c r="H3" s="45"/>
     </row>
-    <row r="4" spans="1:8" s="32" customFormat="1" ht="34.799999999999997">
+    <row r="4" spans="1:8">
       <c r="A4" s="44">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="38" t="s">
-        <v>19</v>
+      <c r="D4" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="E4" s="38">
         <v>255</v>
@@ -2541,7 +2547,7 @@
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="45" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2563,43 +2569,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="48" customWidth="1"/>
-    <col min="2" max="2" width="23.109375" style="48" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" style="48" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" style="48" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" style="48" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" style="48" customWidth="1"/>
-    <col min="7" max="7" width="27.77734375" style="48" customWidth="1"/>
+    <col min="1" max="1" width="7.125" style="48" customWidth="1"/>
+    <col min="2" max="2" width="23.125" style="48" customWidth="1"/>
+    <col min="3" max="3" width="17.75" style="48" customWidth="1"/>
+    <col min="4" max="4" width="22.625" style="48" customWidth="1"/>
+    <col min="5" max="6" width="15.5" style="48" customWidth="1"/>
+    <col min="7" max="7" width="27.75" style="48" customWidth="1"/>
     <col min="8" max="8" width="59" style="42" customWidth="1"/>
-    <col min="9" max="16384" width="12.6640625" style="48"/>
+    <col min="9" max="16384" width="12.625" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="48" customFormat="1" ht="34.799999999999997">
+    <row r="1" spans="1:8">
       <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="D1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="E1" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="F1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="G1" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="H1" s="37" t="s">
         <v>26</v>
-      </c>
-      <c r="H1" s="37" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="46" customFormat="1">
@@ -2607,13 +2612,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">
@@ -2622,18 +2627,18 @@
       <c r="G2" s="39"/>
       <c r="H2" s="14"/>
     </row>
-    <row r="3" spans="1:8" s="48" customFormat="1">
+    <row r="3" spans="1:8">
       <c r="A3" s="44">
         <v>3</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="47" t="s">
-        <v>19</v>
+        <v>50</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="47" t="s">
@@ -2642,18 +2647,18 @@
       <c r="G3" s="49"/>
       <c r="H3" s="14"/>
     </row>
-    <row r="4" spans="1:8" s="48" customFormat="1">
+    <row r="4" spans="1:8">
       <c r="A4" s="44">
         <v>5</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="47" t="s">
-        <v>43</v>
+        <v>52</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>100</v>
       </c>
       <c r="E4" s="47"/>
       <c r="F4" s="47" t="s">
@@ -2664,18 +2669,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="48" customFormat="1" ht="34.799999999999997">
+    <row r="5" spans="1:8">
       <c r="A5" s="44">
         <v>6</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>19</v>
+      <c r="D5" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="E5" s="47">
         <v>255</v>
@@ -2685,21 +2690,21 @@
       </c>
       <c r="G5" s="29"/>
       <c r="H5" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="48" customFormat="1" ht="27.6" customHeight="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="27.6" customHeight="1">
       <c r="A6" s="50">
         <v>9</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="51" t="s">
-        <v>36</v>
+      <c r="D6" s="52" t="s">
+        <v>99</v>
       </c>
       <c r="E6" s="51"/>
       <c r="F6" s="51" t="s">
@@ -2707,7 +2712,7 @@
       </c>
       <c r="G6" s="15"/>
       <c r="H6" s="15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2729,43 +2734,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:H58"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="24" customWidth="1"/>
-    <col min="2" max="2" width="29.5546875" style="24" customWidth="1"/>
+    <col min="1" max="1" width="7.375" style="24" customWidth="1"/>
+    <col min="2" max="2" width="29.5" style="24" customWidth="1"/>
     <col min="3" max="3" width="25" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" style="35" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" style="35" customWidth="1"/>
-    <col min="6" max="6" width="15.44140625" style="35" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5" style="35" customWidth="1"/>
+    <col min="5" max="5" width="17.125" style="35" customWidth="1"/>
+    <col min="6" max="6" width="15.5" style="35" customWidth="1"/>
+    <col min="7" max="7" width="16.875" style="33" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19" style="24" customWidth="1"/>
-    <col min="9" max="16384" width="8.6640625" style="24"/>
+    <col min="9" max="16384" width="8.625" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="24" customFormat="1" ht="34.799999999999997">
+    <row r="1" spans="1:8" ht="37.5">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="D1" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="E1" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="F1" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="G1" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="H1" s="23" t="s">
         <v>26</v>
-      </c>
-      <c r="H1" s="23" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="31" customFormat="1">
@@ -2773,13 +2778,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="E2" s="28"/>
       <c r="F2" s="27" t="s">
@@ -2793,13 +2798,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="26" t="s">
-        <v>30</v>
-      </c>
       <c r="D3" s="27" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="E3" s="27">
         <v>255</v>
@@ -2815,13 +2820,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="E4" s="28"/>
       <c r="F4" s="27" t="s">
@@ -2835,13 +2840,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="E5" s="28"/>
       <c r="F5" s="27" t="s">
@@ -2855,13 +2860,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="E6" s="28"/>
       <c r="F6" s="27" t="s">
@@ -2875,13 +2880,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="E7" s="28"/>
       <c r="F7" s="27" t="s">
